--- a/data/trans_orig/P78_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P78_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si la persona sustentadora principal trabaja actualmente en 2023</t>
+          <t>Población según si la persona sustentadora principal trabaja actualmente en 2023 (tasa de respuesta: 99,42%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>276531</t>
+          <t>278145</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>327538</t>
+          <t>329819</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>227209</t>
+          <t>229825</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>265225</t>
+          <t>264284</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>517809</t>
+          <t>525177</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>581533</t>
+          <t>584440</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,71%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41542</t>
+          <t>39261</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>92549</t>
+          <t>90935</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24485</t>
+          <t>25426</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62501</t>
+          <t>59885</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>77257</t>
+          <t>74350</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>140981</t>
+          <t>133613</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>20,28%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>350866</t>
+          <t>353396</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>374229</t>
+          <t>374945</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,82 +1088,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>91,81%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>97,4%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>424491</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>406562</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>439928</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>91,93%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>88,05%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>95,27%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>790263</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>771733</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>810393</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>93,33%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>91,15%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>97,22%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>424491</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>408573</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>440591</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>91,93%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>88,48%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>95,41%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>637</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>790263</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>771634</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>809330</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>93,33%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>91,13%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,71%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10711</t>
+          <t>9995</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>34074</t>
+          <t>31544</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,82 +1201,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>8,19%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>37274</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>21837</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>55203</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>8,07%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>4,73%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>11,95%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>56442</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>36312</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>74972</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>6,67%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>4,29%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>8,85%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>37274</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>21174</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>53192</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>8,07%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>4,59%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>11,52%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>56442</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>37375</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>75071</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>6,67%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>4,41%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>462484</t>
+          <t>462014</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>474891</t>
+          <t>475163</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>433726</t>
+          <t>433245</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>449717</t>
+          <t>449304</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>901794</t>
+          <t>901090</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>921739</t>
+          <t>922140</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,64%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>4154</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16833</t>
+          <t>17303</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15423</t>
+          <t>15836</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31414</t>
+          <t>31895</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22718</t>
+          <t>22317</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>42663</t>
+          <t>43367</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>749417</t>
+          <t>748432</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>777486</t>
+          <t>777420</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>567011</t>
+          <t>567822</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>588057</t>
+          <t>587771</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1322641</t>
+          <t>1321537</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1368194</t>
+          <t>1367292</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,52%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7754</t>
+          <t>7820</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35823</t>
+          <t>36808</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>28746</t>
+          <t>29032</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>49792</t>
+          <t>48981</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>33850</t>
+          <t>34752</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>79403</t>
+          <t>80507</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>301043</t>
+          <t>300920</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>312792</t>
+          <t>313106</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>282767</t>
+          <t>283192</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>309466</t>
+          <t>310257</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>590031</t>
+          <t>589426</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>620479</t>
+          <t>620923</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,79%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4119</t>
+          <t>3805</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15868</t>
+          <t>15991</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>97408</t>
+          <t>96617</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>124107</t>
+          <t>123682</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>103307</t>
+          <t>102863</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>133755</t>
+          <t>134360</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,56%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19117</t>
+          <t>18633</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25599</t>
+          <t>25631</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9288</t>
+          <t>8752</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>65733</t>
+          <t>67253</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14815</t>
+          <t>16867</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>105826</t>
+          <t>105564</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,46%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3467</t>
+          <t>3435</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9949</t>
+          <t>10433</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>336749</t>
+          <t>335229</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>393194</t>
+          <t>393730</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>325722</t>
+          <t>325984</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>416733</t>
+          <t>414681</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,09%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>741</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>4355</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16709</t>
+          <t>16452</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30213</t>
+          <t>29963</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18850</t>
+          <t>18675</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>32745</t>
+          <t>32744</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>980</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4594</t>
+          <t>4590</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>198761</t>
+          <t>199011</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>212265</t>
+          <t>212522</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>201564</t>
+          <t>201565</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>215459</t>
+          <t>215634</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,03%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2201831</t>
+          <t>2200055</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2279414</t>
+          <t>2279383</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1435238</t>
+          <t>1615442</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2215378</t>
+          <t>2223083</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3739116</t>
+          <t>3712386</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4491567</t>
+          <t>4486477</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,59%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>90475</t>
+          <t>90506</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>168058</t>
+          <t>169834</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>656370</t>
+          <t>648665</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1436510</t>
+          <t>1256306</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>750070</t>
+          <t>755160</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1502521</t>
+          <t>1529251</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>29,18%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P78_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P78_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>307985</t>
+          <t>320318</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>278145</t>
+          <t>295685</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>329819</t>
+          <t>340375</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>248523</t>
+          <t>294254</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>229825</t>
+          <t>275373</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>264284</t>
+          <t>310191</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>556508</t>
+          <t>614572</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>525177</t>
+          <t>584366</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>584440</t>
+          <t>639824</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>90,21%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>61095</t>
+          <t>54027</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39261</t>
+          <t>33970</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>90935</t>
+          <t>78660</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>41187</t>
+          <t>40634</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25426</t>
+          <t>24697</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59885</t>
+          <t>59515</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>102282</t>
+          <t>94661</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>74350</t>
+          <t>69409</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>133613</t>
+          <t>124867</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>17,61%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>369080</t>
+          <t>374345</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>369080</t>
+          <t>374345</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>369080</t>
+          <t>374345</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289710</t>
+          <t>334888</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289710</t>
+          <t>334888</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289710</t>
+          <t>334888</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>658790</t>
+          <t>709233</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>658790</t>
+          <t>709233</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>658790</t>
+          <t>709233</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>365772</t>
+          <t>417813</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>353396</t>
+          <t>404897</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>374945</t>
+          <t>427950</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>424491</t>
+          <t>406713</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>406562</t>
+          <t>389146</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>439928</t>
+          <t>417768</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>790263</t>
+          <t>824526</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>771733</t>
+          <t>805781</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>810393</t>
+          <t>840085</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,32%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>19168</t>
+          <t>19535</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9995</t>
+          <t>9398</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31544</t>
+          <t>32451</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>37274</t>
+          <t>37227</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21837</t>
+          <t>26172</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>55203</t>
+          <t>54794</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>56442</t>
+          <t>56762</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>36312</t>
+          <t>41203</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>74972</t>
+          <t>75507</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>384940</t>
+          <t>437348</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>384940</t>
+          <t>437348</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>384940</t>
+          <t>437348</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>461765</t>
+          <t>443940</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>461765</t>
+          <t>443940</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>461765</t>
+          <t>443940</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>846705</t>
+          <t>881288</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>846705</t>
+          <t>881288</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>846705</t>
+          <t>881288</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>470296</t>
+          <t>546666</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>462014</t>
+          <t>538268</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>475163</t>
+          <t>551708</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>442338</t>
+          <t>508076</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>433245</t>
+          <t>499353</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>449304</t>
+          <t>515550</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>912634</t>
+          <t>1054743</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>901090</t>
+          <t>1043525</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>922140</t>
+          <t>1063669</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,71%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9021</t>
+          <t>9585</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4154</t>
+          <t>4543</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17303</t>
+          <t>17983</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22802</t>
+          <t>24254</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15836</t>
+          <t>16780</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31895</t>
+          <t>32977</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>31823</t>
+          <t>33839</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22317</t>
+          <t>24913</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>43367</t>
+          <t>45057</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>479317</t>
+          <t>556251</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>479317</t>
+          <t>556251</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>479317</t>
+          <t>556251</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>465140</t>
+          <t>532330</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>465140</t>
+          <t>532330</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>465140</t>
+          <t>532330</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>944457</t>
+          <t>1088582</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>944457</t>
+          <t>1088582</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>944457</t>
+          <t>1088582</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>763896</t>
+          <t>563425</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>748432</t>
+          <t>549808</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>777420</t>
+          <t>572433</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>578537</t>
+          <t>588581</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>567822</t>
+          <t>577936</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>587771</t>
+          <t>599056</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1342434</t>
+          <t>1152006</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1321537</t>
+          <t>1135947</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1367292</t>
+          <t>1165757</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>95,84%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>21344</t>
+          <t>23124</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7820</t>
+          <t>14116</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36808</t>
+          <t>36741</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>41256</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29032</t>
+          <t>30781</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>48981</t>
+          <t>51901</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>59610</t>
+          <t>64380</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>34752</t>
+          <t>50629</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>80507</t>
+          <t>80439</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>785240</t>
+          <t>586549</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>785240</t>
+          <t>586549</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>785240</t>
+          <t>586549</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>616803</t>
+          <t>629837</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>616803</t>
+          <t>629837</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>616803</t>
+          <t>629837</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1402044</t>
+          <t>1216386</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1402044</t>
+          <t>1216386</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1402044</t>
+          <t>1216386</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>308805</t>
+          <t>341573</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>300920</t>
+          <t>333440</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>313106</t>
+          <t>346511</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>296819</t>
+          <t>329676</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>283192</t>
+          <t>314543</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>310257</t>
+          <t>343944</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>605625</t>
+          <t>671249</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>589426</t>
+          <t>655416</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>620923</t>
+          <t>690250</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>86,08%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8106</t>
+          <t>10005</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>5067</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15991</t>
+          <t>18138</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>110055</t>
+          <t>120620</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>96617</t>
+          <t>106352</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>123682</t>
+          <t>135753</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>118161</t>
+          <t>130625</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>102863</t>
+          <t>111624</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>134360</t>
+          <t>146458</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,26%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>316911</t>
+          <t>351578</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>316911</t>
+          <t>351578</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>316911</t>
+          <t>351578</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>406874</t>
+          <t>450296</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>406874</t>
+          <t>450296</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>406874</t>
+          <t>450296</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>723786</t>
+          <t>801874</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>723786</t>
+          <t>801874</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>723786</t>
+          <t>801874</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>22636</t>
+          <t>25367</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18633</t>
+          <t>21221</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25631</t>
+          <t>28837</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>30293</t>
+          <t>34651</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8752</t>
+          <t>27847</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>67253</t>
+          <t>43594</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>52929</t>
+          <t>60017</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16867</t>
+          <t>50305</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>105564</t>
+          <t>70855</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>28,92%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>6430</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3435</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10433</t>
+          <t>11461</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>372189</t>
+          <t>177652</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>335229</t>
+          <t>168709</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>393730</t>
+          <t>184456</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>378619</t>
+          <t>184968</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>325984</t>
+          <t>174130</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>414681</t>
+          <t>194680</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>79,47%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>29066</t>
+          <t>32682</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>29066</t>
+          <t>32682</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>29066</t>
+          <t>32682</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>402482</t>
+          <t>212303</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>402482</t>
+          <t>212303</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>402482</t>
+          <t>212303</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>431548</t>
+          <t>244985</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>431548</t>
+          <t>244985</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>431548</t>
+          <t>244985</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>2712</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>858</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4355</t>
+          <t>4545</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>22432</t>
+          <t>24514</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16452</t>
+          <t>18017</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29963</t>
+          <t>31454</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>24899</t>
+          <t>27226</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18675</t>
+          <t>19633</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>32744</t>
+          <t>35253</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,9%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4590</t>
+          <t>4781</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>206542</t>
+          <t>223397</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>199011</t>
+          <t>216457</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>212522</t>
+          <t>229894</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>209410</t>
+          <t>226324</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>201565</t>
+          <t>218297</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>215634</t>
+          <t>233917</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,26%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>5639</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>5639</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>5639</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>228974</t>
+          <t>247911</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>228974</t>
+          <t>247911</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>228974</t>
+          <t>247911</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>234309</t>
+          <t>253550</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>234309</t>
+          <t>253550</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>234309</t>
+          <t>253550</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,17 +3126,17 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2241856</t>
+          <t>2217872</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2200055</t>
+          <t>2183529</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2279383</t>
+          <t>2244972</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2043434</t>
+          <t>2186466</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1615442</t>
+          <t>2146726</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2223083</t>
+          <t>2227347</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>4285290</t>
+          <t>4404338</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3712386</t>
+          <t>4351225</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4486477</t>
+          <t>4453396</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,71%</t>
         </is>
       </c>
     </row>
@@ -3239,17 +3239,17 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>128033</t>
+          <t>126520</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>90506</t>
+          <t>99420</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>169834</t>
+          <t>160863</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>828314</t>
+          <t>665039</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>648665</t>
+          <t>624158</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1256306</t>
+          <t>704779</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>956347</t>
+          <t>791559</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>755160</t>
+          <t>742501</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1529251</t>
+          <t>844672</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>16,26%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2369889</t>
+          <t>2344392</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2369889</t>
+          <t>2344392</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2369889</t>
+          <t>2344392</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2871748</t>
+          <t>2851505</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2871748</t>
+          <t>2851505</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2871748</t>
+          <t>2851505</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>5241637</t>
+          <t>5195897</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>5241637</t>
+          <t>5195897</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>5241637</t>
+          <t>5195897</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
